--- a/Intersecciones/excels/CAJAMARCA-JAEN-BELLAVISTA.xlsx
+++ b/Intersecciones/excels/CAJAMARCA-JAEN-BELLAVISTA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,7 +483,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>l-289741</t>
+          <t>I-289715</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -508,22 +508,22 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-5.6657194</t>
+          <t>-5.6621995</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-78.680398</t>
+          <t>-78.6781168</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -535,7 +535,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>l-289759</t>
+          <t>I-668047</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -560,22 +560,22 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-5.6651289</t>
+          <t>-5.5382823</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-78.6811403</t>
+          <t>-78.8228012</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -587,7 +587,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>l-289773</t>
+          <t>I-645635</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -612,22 +612,22 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-5.6657012</t>
+          <t>-5.4488502</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-78.6804195</t>
+          <t>-78.8319386</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -639,7 +639,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>l-565468</t>
+          <t>I-635754</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -664,25 +664,285 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-5.6649013</t>
+          <t>-5.5398061</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-78.6808325</t>
+          <t>-78.8002431</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
+        <is>
+          <t>060802</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>I-668844</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>060802</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>JAEN</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>BELLAVISTA</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>-5.5746117</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-78.8050631</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Calle Alfonso Ugarte / Jirón José Faustino Sánchez Carrión</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>060802</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>I-668849</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>060802</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>JAEN</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>BELLAVISTA</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>-5.5726436</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-78.8043944</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Calle José Faustino Sánchez Carrión / Jirón Sucre</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>060802</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>I-668851</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>060802</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>JAEN</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>BELLAVISTA</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>-5.573632</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-78.8054248</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Avenida Mariscal Castilla / Jirón Unión</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>060802</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>I-635708</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>060802</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>JAEN</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>BELLAVISTA</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>-5.5438506</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-78.7999937</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>060802</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>I-569245</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>060802</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>JAEN</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>BELLAVISTA</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>-5.5531543</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-78.8072544</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
         <is>
           <t>060802</t>
         </is>

--- a/Intersecciones/excels/CAJAMARCA-JAEN-BELLAVISTA.xlsx
+++ b/Intersecciones/excels/CAJAMARCA-JAEN-BELLAVISTA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -948,6 +948,266 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>I-289440</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>060802</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>JAEN</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>BELLAVISTA</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>-5.5822146</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-78.7790387</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>060802</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>I-617001</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>060802</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>JAEN</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>BELLAVISTA</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>-5.6860857</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-78.7628397</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>060802</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>I-624573</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>060802</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>JAEN</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>BELLAVISTA</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>-5.5104802</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-78.6247403</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>060802</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>I-624574</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>060802</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>JAEN</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>BELLAVISTA</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>-5.5098535</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-78.6244996</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>060802</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>I-624576</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>060802</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>JAEN</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>BELLAVISTA</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>-5.5093562</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-78.6257721</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>060802</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Intersecciones/excels/CAJAMARCA-JAEN-BELLAVISTA.xlsx
+++ b/Intersecciones/excels/CAJAMARCA-JAEN-BELLAVISTA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1208,6 +1208,474 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>I-635704</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>060802</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>JAEN</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>BELLAVISTA</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>-5.5414559</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-78.7995806</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>060802</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>I-635624</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>060802</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>JAEN</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>BELLAVISTA</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>-5.5106251</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-78.6261757</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>060802</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>I-635633</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>060802</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>JAEN</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>BELLAVISTA</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-5.587175</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-78.7866417</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Calle Ucayali / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>060802</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>I-635634</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>060802</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>JAEN</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>BELLAVISTA</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>-5.5886245</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-78.7865344</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>060802</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>I-635635</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>060802</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>JAEN</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>BELLAVISTA</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>-5.5874339</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-78.7863761</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Calle Ucayali / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>060802</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>I-635636</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>060802</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>JAEN</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>BELLAVISTA</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>-5.5854519</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-78.7847083</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>060802</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>I-635706</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>060802</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>JAEN</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>BELLAVISTA</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>-5.5406497</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-78.7995887</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>060802</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>I-624568</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>060802</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>JAEN</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>BELLAVISTA</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>-5.5088243</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-78.6276231</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>060802</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>I-668053</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>060802</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>JAEN</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>BELLAVISTA</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>-5.5069471</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-78.7829222</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>060802</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Intersecciones/excels/CAJAMARCA-JAEN-BELLAVISTA.xlsx
+++ b/Intersecciones/excels/CAJAMARCA-JAEN-BELLAVISTA.xlsx
@@ -425,35 +425,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>ubigeo_gestor</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>PROVINCIA</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>DISTRITO</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>ID_INT</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>UBIGEO</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>DEPARTAMENTO</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>PROVINCIA</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>DISTRITO</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>LATITUD</t>
@@ -472,40 +472,35 @@
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Siniestro_fatal</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>ubigeo_gestor</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>060802</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>JAEN</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>BELLAVISTA</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>I-289715</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>060802</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>CAJAMARCA</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>JAEN</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>BELLAVISTA</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>-5.6621995</t>
@@ -524,40 +519,35 @@
       <c r="I2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>060802</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>060802</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>JAEN</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>BELLAVISTA</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>I-668047</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>060802</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>CAJAMARCA</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>JAEN</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>BELLAVISTA</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>-5.5382823</t>
@@ -576,40 +566,35 @@
       <c r="I3" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>060802</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>060802</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>JAEN</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>BELLAVISTA</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>I-645635</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>060802</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>CAJAMARCA</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>JAEN</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>BELLAVISTA</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>-5.4488502</t>
@@ -628,40 +613,35 @@
       <c r="I4" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>060802</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>060802</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>JAEN</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>BELLAVISTA</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>I-635754</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>060802</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>CAJAMARCA</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>JAEN</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>BELLAVISTA</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>-5.5398061</t>
@@ -680,40 +660,35 @@
       <c r="I5" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>060802</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>060802</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>JAEN</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>BELLAVISTA</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>I-668844</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>060802</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>CAJAMARCA</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>JAEN</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>BELLAVISTA</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>-5.5746117</t>
@@ -732,40 +707,35 @@
       <c r="I6" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>060802</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>060802</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>JAEN</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>BELLAVISTA</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>I-668849</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>060802</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>CAJAMARCA</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>JAEN</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>BELLAVISTA</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>-5.5726436</t>
@@ -784,40 +754,35 @@
       <c r="I7" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>060802</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>060802</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>JAEN</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>BELLAVISTA</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>I-668851</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>060802</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>CAJAMARCA</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>JAEN</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>BELLAVISTA</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>-5.573632</t>
@@ -836,40 +801,35 @@
       <c r="I8" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>060802</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>060802</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>JAEN</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>BELLAVISTA</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>I-635708</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>060802</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>CAJAMARCA</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>JAEN</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>BELLAVISTA</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>-5.5438506</t>
@@ -888,40 +848,35 @@
       <c r="I9" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>060802</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>060802</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>JAEN</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>BELLAVISTA</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>I-569245</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>060802</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>CAJAMARCA</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>JAEN</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>BELLAVISTA</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>-5.5531543</t>
@@ -940,40 +895,35 @@
       <c r="I10" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>060802</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>060802</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>JAEN</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>BELLAVISTA</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>I-289440</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>060802</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>CAJAMARCA</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>JAEN</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>BELLAVISTA</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>-5.5822146</t>
@@ -992,40 +942,35 @@
       <c r="I11" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>060802</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>060802</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>JAEN</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>BELLAVISTA</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>I-617001</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>060802</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>CAJAMARCA</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>JAEN</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>BELLAVISTA</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>-5.6860857</t>
@@ -1044,40 +989,35 @@
       <c r="I12" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>060802</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>060802</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>JAEN</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>BELLAVISTA</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>I-624573</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>060802</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>CAJAMARCA</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>JAEN</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>BELLAVISTA</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>-5.5104802</t>
@@ -1096,40 +1036,35 @@
       <c r="I13" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>060802</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>060802</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>JAEN</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>BELLAVISTA</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>I-624574</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>060802</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>CAJAMARCA</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>JAEN</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>BELLAVISTA</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>-5.5098535</t>
@@ -1148,40 +1083,35 @@
       <c r="I14" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>060802</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>060802</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>JAEN</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>BELLAVISTA</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>I-624576</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>060802</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>CAJAMARCA</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>JAEN</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>BELLAVISTA</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>-5.5093562</t>
@@ -1200,40 +1130,35 @@
       <c r="I15" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>060802</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>060802</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>JAEN</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>BELLAVISTA</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>I-635704</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>060802</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>CAJAMARCA</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>JAEN</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>BELLAVISTA</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>-5.5414559</t>
@@ -1252,40 +1177,35 @@
       <c r="I16" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>060802</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>060802</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>JAEN</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>BELLAVISTA</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>I-635624</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>060802</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>CAJAMARCA</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>JAEN</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>BELLAVISTA</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>-5.5106251</t>
@@ -1304,40 +1224,35 @@
       <c r="I17" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>060802</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>060802</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>JAEN</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>BELLAVISTA</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>I-635633</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>060802</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>CAJAMARCA</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>JAEN</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>BELLAVISTA</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>-5.587175</t>
@@ -1356,40 +1271,35 @@
       <c r="I18" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>060802</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>060802</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>JAEN</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>BELLAVISTA</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>I-635634</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>060802</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>CAJAMARCA</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>JAEN</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>BELLAVISTA</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>-5.5886245</t>
@@ -1408,40 +1318,35 @@
       <c r="I19" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>060802</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>060802</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>JAEN</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>BELLAVISTA</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>I-635635</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>060802</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>CAJAMARCA</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>JAEN</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>BELLAVISTA</t>
-        </is>
-      </c>
       <c r="F20" t="inlineStr">
         <is>
           <t>-5.5874339</t>
@@ -1460,40 +1365,35 @@
       <c r="I20" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>060802</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>060802</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>JAEN</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>BELLAVISTA</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>I-635636</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>060802</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>CAJAMARCA</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>JAEN</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>BELLAVISTA</t>
-        </is>
-      </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>-5.5854519</t>
@@ -1512,40 +1412,35 @@
       <c r="I21" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>060802</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>060802</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>JAEN</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>BELLAVISTA</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>I-635706</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>060802</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>CAJAMARCA</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>JAEN</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>BELLAVISTA</t>
-        </is>
-      </c>
       <c r="F22" t="inlineStr">
         <is>
           <t>-5.5406497</t>
@@ -1564,40 +1459,35 @@
       <c r="I22" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>060802</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>060802</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>JAEN</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>BELLAVISTA</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>I-624568</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>060802</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>CAJAMARCA</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>JAEN</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>BELLAVISTA</t>
-        </is>
-      </c>
       <c r="F23" t="inlineStr">
         <is>
           <t>-5.5088243</t>
@@ -1616,40 +1506,35 @@
       <c r="I23" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>060802</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>060802</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>JAEN</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>BELLAVISTA</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>I-668053</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>060802</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>CAJAMARCA</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>JAEN</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>BELLAVISTA</t>
-        </is>
-      </c>
       <c r="F24" t="inlineStr">
         <is>
           <t>-5.5069471</t>
@@ -1668,11 +1553,6 @@
       <c r="I24" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>060802</t>
         </is>
       </c>
     </row>

--- a/Intersecciones/excels/CAJAMARCA-JAEN-BELLAVISTA.xlsx
+++ b/Intersecciones/excels/CAJAMARCA-JAEN-BELLAVISTA.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ID_INT</t>
+          <t>Codigo</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">

--- a/Intersecciones/excels/CAJAMARCA-JAEN-BELLAVISTA.xlsx
+++ b/Intersecciones/excels/CAJAMARCA-JAEN-BELLAVISTA.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,51 +413,51 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>DEPARTAMENTO</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>PROVINCIA</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>DISTRITO</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Codigo</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>LATITUD</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>LONGITUD</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Vias</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Siniestro_fatal</t>
         </is>
@@ -1551,6 +1539,429 @@
         </is>
       </c>
       <c r="I24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>060802</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>JAEN</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>BELLAVISTA</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>I-289711</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>-5.6648184</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-78.676688</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>CA. VILLANUEVA PINILLOS Y CA. DANIEL ALCIDES CARRION</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>060802</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>JAEN</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>BELLAVISTA</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>I-289723</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>-5.6675473</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-78.6765718</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>CA. SANTA ROSA Y CA. ALFONSO UGARTE</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>060802</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>JAEN</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>BELLAVISTA</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>I-289725</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>-5.6650079</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-78.6738683</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>CA. SANTA ROSA Y VIA PUERTO MARAÑON</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>060802</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>JAEN</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>BELLAVISTA</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>I-289740</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>-5.6649927</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-78.6789436</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>CA. GARCILAZO DE LA VEGA Y CA. SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>060802</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>JAEN</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>BELLAVISTA</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>I-289741</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>-5.6657194</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-78.680398</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>AV. MESONES MURO Y CA. GARCILAZO DE LA VEGA</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>060802</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>JAEN</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>BELLAVISTA</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>I-289768</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>-5.6522658</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-78.703819</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>AV. JAEN - CRUCE A SECTOR LA CAPILLA</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>060802</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>JAEN</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>BELLAVISTA</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>I-289769</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>-5.6521375</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-78.7014334</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>AV. JAEN Y JR. TAMBORAPA</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>060802</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>JAEN</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>BELLAVISTA</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>I-586506</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>-5.6638265</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-78.6829568</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>AV. MESONES MURO Y CA. CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>060802</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>JAEN</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>BELLAVISTA</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>I-725187</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>-5.6511359</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-78.7426092</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>INGRESO A BELLAVISTA - CRUCE SHANANGO</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/Intersecciones/excels/CAJAMARCA-JAEN-BELLAVISTA.xlsx
+++ b/Intersecciones/excels/CAJAMARCA-JAEN-BELLAVISTA.xlsx
@@ -491,12 +491,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-5.6621995</t>
+          <t>-5.666304</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-78.6781168</t>
+          <t>-78.675716</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -538,12 +538,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-5.5382823</t>
+          <t>-5.663756</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-78.8228012</t>
+          <t>-78.680585</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -726,17 +726,17 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-5.5726436</t>
+          <t>-5.668665</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-78.8043944</t>
+          <t>-78.678107</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Calle José Faustino Sánchez Carrión / Jirón Sucre</t>
+          <t>Calle Santa Rosa / Av. Mesones Muro</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -773,17 +773,17 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-5.573632</t>
+          <t>-5.667396</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-78.8054248</t>
+          <t>-78.678671</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Avenida Mariscal Castilla / Jirón Unión</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1149,17 +1149,17 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-5.5414559</t>
+          <t>-5.663812</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-78.7995806</t>
+          <t>-78.678505</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Calle Alfonso Ugarte / Calle s / n</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1243,17 +1243,17 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-5.587175</t>
+          <t>-5.651958</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-78.7866417</t>
+          <t>-78.699712</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Calle Ucayali / Calle s / n</t>
+          <t>Av. Jaen / Calle s / n</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1290,17 +1290,17 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-5.5886245</t>
+          <t>-5.666142</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-78.7865344</t>
+          <t>-78.678232</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Calle San Martin / Calle Arica</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">

--- a/Intersecciones/excels/CAJAMARCA-JAEN-BELLAVISTA.xlsx
+++ b/Intersecciones/excels/CAJAMARCA-JAEN-BELLAVISTA.xlsx
@@ -486,22 +486,22 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>I-289715</t>
+          <t>I-725187</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-5.666304</t>
+          <t>-5.6511359</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-78.675716</t>
+          <t>-78.7426092</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>INGRESO A BELLAVISTA - CRUCE SHANANGO</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -533,17 +533,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>I-668047</t>
+          <t>I-668851</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-5.663756</t>
+          <t>-5.667396</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-78.680585</t>
+          <t>-78.678671</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -580,22 +580,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>I-645635</t>
+          <t>I-668849</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-5.4488502</t>
+          <t>-5.668665</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-78.8319386</t>
+          <t>-78.678107</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Calle Santa Rosa / Av. Mesones Muro</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -627,22 +627,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>I-635754</t>
+          <t>I-668844</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-5.5398061</t>
+          <t>-5.5746117</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-78.8002431</t>
+          <t>-78.8050631</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Calle Alfonso Ugarte / Jirón José Faustino Sánchez Carrión</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -674,22 +674,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>I-668844</t>
+          <t>I-668053</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-5.5746117</t>
+          <t>-5.5069471</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-78.8050631</t>
+          <t>-78.7829222</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Calle Alfonso Ugarte / Jirón José Faustino Sánchez Carrión</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -721,22 +721,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>I-668849</t>
+          <t>I-668047</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-5.668665</t>
+          <t>-5.663756</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-78.678107</t>
+          <t>-78.680585</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Calle Santa Rosa / Av. Mesones Muro</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -768,17 +768,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>I-668851</t>
+          <t>I-645635</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-5.667396</t>
+          <t>-5.4488502</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-78.678671</t>
+          <t>-78.8319386</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -815,17 +815,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>I-635708</t>
+          <t>I-635754</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-5.5438506</t>
+          <t>-5.5398061</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-78.7999937</t>
+          <t>-78.8002431</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -862,17 +862,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>I-569245</t>
+          <t>I-635708</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-5.5531543</t>
+          <t>-5.5438506</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-78.8072544</t>
+          <t>-78.7999937</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -909,17 +909,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>I-289440</t>
+          <t>I-635706</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-5.5822146</t>
+          <t>-5.5406497</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-78.7790387</t>
+          <t>-78.7995887</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -956,22 +956,22 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>I-617001</t>
+          <t>I-635704</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-5.6860857</t>
+          <t>-5.663812</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-78.7628397</t>
+          <t>-78.678505</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Calle Alfonso Ugarte / Calle s / n</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1003,17 +1003,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>I-624573</t>
+          <t>I-635636</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-5.5104802</t>
+          <t>-5.5854519</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-78.6247403</t>
+          <t>-78.7847083</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1050,22 +1050,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>I-624574</t>
+          <t>I-635635</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-5.5098535</t>
+          <t>-5.5874339</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-78.6244996</t>
+          <t>-78.7863761</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Calle Ucayali / Calle s / n</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1097,22 +1097,22 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>I-624576</t>
+          <t>I-635634</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-5.5093562</t>
+          <t>-5.666142</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-78.6257721</t>
+          <t>-78.678232</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Calle San Martin / Calle Arica</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1144,22 +1144,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>I-635704</t>
+          <t>I-635633</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-5.663812</t>
+          <t>-5.651958</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-78.678505</t>
+          <t>-78.699712</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Calle Alfonso Ugarte / Calle s / n</t>
+          <t>Av. Jaen / Calle s / n</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1238,22 +1238,22 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>I-635633</t>
+          <t>I-624576</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-5.651958</t>
+          <t>-5.5093562</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-78.699712</t>
+          <t>-78.6257721</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Av. Jaen / Calle s / n</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1285,22 +1285,22 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>I-635634</t>
+          <t>I-624574</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-5.666142</t>
+          <t>-5.5098535</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-78.678232</t>
+          <t>-78.6244996</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Calle San Martin / Calle Arica</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1332,22 +1332,22 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>I-635635</t>
+          <t>I-624573</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-5.5874339</t>
+          <t>-5.5104802</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-78.7863761</t>
+          <t>-78.6247403</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Calle Ucayali / Calle s / n</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1379,17 +1379,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>I-635636</t>
+          <t>I-624568</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-5.5854519</t>
+          <t>-5.5088243</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-78.7847083</t>
+          <t>-78.6276231</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1426,17 +1426,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>I-635706</t>
+          <t>I-617001</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-5.5406497</t>
+          <t>-5.6860857</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-78.7995887</t>
+          <t>-78.7628397</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1473,22 +1473,22 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>I-624568</t>
+          <t>I-586506</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-5.5088243</t>
+          <t>-5.6638265</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-78.6276231</t>
+          <t>-78.6829568</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>AV. MESONES MURO Y CA. CAJAMARCA</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1520,17 +1520,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>I-668053</t>
+          <t>I-569245</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-5.5069471</t>
+          <t>-5.5531543</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-78.7829222</t>
+          <t>-78.8072544</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1567,22 +1567,22 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>I-289711</t>
+          <t>I-289769</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-5.6648184</t>
+          <t>-5.6521375</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-78.676688</t>
+          <t>-78.7014334</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>CA. VILLANUEVA PINILLOS Y CA. DANIEL ALCIDES CARRION</t>
+          <t>AV. JAEN Y JR. TAMBORAPA</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1614,22 +1614,22 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>I-289723</t>
+          <t>I-289768</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-5.6675473</t>
+          <t>-5.6522658</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-78.6765718</t>
+          <t>-78.703819</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>CA. SANTA ROSA Y CA. ALFONSO UGARTE</t>
+          <t>AV. JAEN - CRUCE A SECTOR LA CAPILLA</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1661,22 +1661,22 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>I-289725</t>
+          <t>I-289741</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-5.6650079</t>
+          <t>-5.6657194</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-78.6738683</t>
+          <t>-78.680398</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>CA. SANTA ROSA Y VIA PUERTO MARAÑON</t>
+          <t>AV. MESONES MURO Y CA. GARCILAZO DE LA VEGA</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1755,22 +1755,22 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>I-289741</t>
+          <t>I-289725</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-5.6657194</t>
+          <t>-5.6650079</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-78.680398</t>
+          <t>-78.6738683</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>AV. MESONES MURO Y CA. GARCILAZO DE LA VEGA</t>
+          <t>CA. SANTA ROSA Y VIA PUERTO MARAÑON</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1802,22 +1802,22 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>I-289768</t>
+          <t>I-289723</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-5.6522658</t>
+          <t>-5.6675473</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-78.703819</t>
+          <t>-78.6765718</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>AV. JAEN - CRUCE A SECTOR LA CAPILLA</t>
+          <t>CA. SANTA ROSA Y CA. ALFONSO UGARTE</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1849,22 +1849,22 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>I-289769</t>
+          <t>I-289715</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-5.6521375</t>
+          <t>-5.666304</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-78.7014334</t>
+          <t>-78.675716</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>AV. JAEN Y JR. TAMBORAPA</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1896,22 +1896,22 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>I-586506</t>
+          <t>I-289711</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-5.6638265</t>
+          <t>-5.6648184</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-78.6829568</t>
+          <t>-78.676688</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>AV. MESONES MURO Y CA. CAJAMARCA</t>
+          <t>CA. VILLANUEVA PINILLOS Y CA. DANIEL ALCIDES CARRION</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1943,22 +1943,22 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>I-725187</t>
+          <t>I-289440</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-5.6511359</t>
+          <t>-5.5822146</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-78.7426092</t>
+          <t>-78.7790387</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>INGRESO A BELLAVISTA - CRUCE SHANANGO</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
